--- a/20260630/알라딘.xlsx
+++ b/20260630/알라딘.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,6 +453,3306 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>화법으로 마스터하는 법인컨설팅 ABC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>김기홍 (지은이)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>15,300원</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>도서출판 위</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026년 4월</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ABC 살인사건</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>애거사 크리스티 (지은이) 유명우 (옮긴이)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>10,800원</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>해문출판사</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2002년 5월</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>i-dle (아이들) - 미니 9집 We made (Gimme Dat Love Ver.)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>i-dle (아이들)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>29,700원</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Kakao Entertainment</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026년 7월</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ABC 살인 사건</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>애거사 크리스티 (지은이) 김남주 (옮긴이)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>10,800원</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>황금가지</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2013년 12월</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>노부영 세이펜 Me! Me! ABC (Paperback + CD)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>해리엣 지퍼트 (지은이) Ingri Von Bergen (그림)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>12,600원</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>JYbooks(제이와이북스)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2016년 4월</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ABC 떼기 1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>기탄교육 편집부 (엮은이)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>5,400원</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>기탄교육</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2008년 8월</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ABC 살인사건</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>애거서 크리스티 (지은이) 유명우 (옮긴이)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>5,400원</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>해문출판사</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1990년 3월</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>7살 첫 영어 : 알파벳 ABC</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>징검다리 교육연구소 (지은이)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>9,900원</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>이지스에듀(이지스퍼블리싱)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2022년 5월</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>음악의 ABC</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>이모겐 홀스트 벤저민 브리튼 (지은이) 이석호 (옮긴이)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>16,200원</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>포노(PHONO)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2018년 5월</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>연주가 좋아지는 음악이론 ABC</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>나경원 (지은이)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>9,000원</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>현대음악출판사(현대교육미디어)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2014년 5월</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Alphabet Ice Cream : A Fantastic Fun-filled ABC (Paperback)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>닉 샤랫 수 힙 (지은이)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8,840원</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Puffin Books</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2007년 5월</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ABC 살인 사건 - 애거서 크리스티 전집 44</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>애거서 크리스티 (지은이) 김남주 (옮긴이)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>9,600원</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>황금가지</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2013년 12월</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ABC 호흡 놀이</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>크리스토퍼 윌라드 다니엘 레흐트샤펀 (지은이) 홀리 클리프턴-브라운 (그림) 이임숙 (옮긴이)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>10,800원</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>불광출판사</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2022년 3월</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>기후변화 ABC</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>다비드 넬스 크리스티안 제러 (지은이) 강영옥 (옮긴이) 남성현 (감수)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>11,700원</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>동녘사이언스</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2021년 6월</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>생각하는 ABC (특별보급판)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>이보나 흐미엘레프스카 (지은이) 이지원 (구성)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>15,120원</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>논장</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2016년 6월</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>어르신을 위한 ABC</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>박이수 김자은 박지우 (지은이) 이지혜 (감수)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>15,000원</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>커뮤니케이션북스</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2007년 12월</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ABC 떼기 2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>기탄교육 편집부 (엮은이)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>5,400원</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>기탄교육</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2008년 8월</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026 해커스공무원 서호성 ABC 경제학 단원별 기출문제집 (7급 공무원, 7급 군무원, 국회직 8급, 통계직 9급)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>서호성 (지은이)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>42,300원</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>해커스공무원</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026년 1월</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>사회주의 ABC</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>바스카 순카라 에릭 올린 라이트 (지은이) 한형식 (옮긴이)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>12,600원</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>나름북스</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2017년 1월</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Eric Carle's ABC (Hardcover)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>에릭 칼 (지은이)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>11,440원</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Grosset &amp; Dunlap</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2007년 5월</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>랄랄라 사운드 벽보 7 : ABC</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>아이키움북 편집부 (지은이)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>4,500원</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>아이키움북</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2017년 9월</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Magic ABC 초등 영어회화 첫걸음</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Lina 이동호 (지은이)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>16,200원</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>국제어학연구소(좋은글)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2023년 12월</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ABC, 민중의 마음이 문자가 되다</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>이반 일리치 배리 샌더스 (지은이) 권루시안 (옮긴이) 장지연 (감수)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>14,400원</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>문학동네</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2016년 9월</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dr. Seuss's ABC: An Amazing Alphabet Book! (Board Books)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>닥터 수스 Dr. Seuss (지은이)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>7,120원</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Random House Childrens Books</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1996년 11월</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ABC 떼기 3</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>기탄교육 편집부 (엮은이)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>5,400원</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>기탄교육</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2008년 8월</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>전자기학의 ABC</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>후쿠시마 하지메 (지은이) 손영수 (옮긴이)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>15,960원</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>전파과학사</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2019년 2월</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ABC 알파벳 쓰기</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>넥서스콘텐츠개발팀 (지은이)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>9,900원</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>넥서스Friends</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2023년 11월</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ABC 호텔: 노래하는 영어 동시</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>마리 앤 호버맨 (지은이) 말라 프레이지 (그림) 한지원 (옮긴이)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>17,100원</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>윌북주니어</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2025년 10월</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026 해커스공무원 서호성 ABC 경제학 기본서 (7급 공무원, 7급 군무원, 국회직 8급, 통계직 9급)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>서호성 (지은이)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>45,900원</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>해커스공무원</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026년 1월</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>상대성이론 ABC</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>버트런드 러셀 (지은이) 권혁 (옮긴이)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>13,500원</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>돋을새김</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2024년 10월</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>벅스 ABC</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>난주 (지은이)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>17,100원</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>고래뱃속</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2023년 4월</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>abc 26 Letters</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>플래시덕 연구팀 (엮은이)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>5,400원</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>라잇트브릿지(리틀스텝)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2014년 3월</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>마케팅원론 ABC</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>김상용 송재도 양재호 원지성 윤호정 송태호 김태완 김지윤 송시연 김모란 (지은이)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>29,000원</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>학지사</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2022년 9월</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Smart ABC Book (Paperback)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Soo Kim (지은이)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>9,900원</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>e-future</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2023년 12월</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>노부영 세이펜 Me! Me! ABC (Paperback)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>해리엣 지퍼트 (지은이) Ingri Von Bergen (그림)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>9,900원</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>JYbooks(제이와이북스)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2013년 1월</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ABC 살인사건</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>애거서 크리스티 (지은이) 박순녀 (옮긴이)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>6,120원</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>동서문화동판(동서문화사)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2003년 1월</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Museum ABC (Hardcover)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>메트로폴리탄 미술관 (지은이)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>20,720원</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Little Brown Books</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2002년 9월</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Dr. Seuss's ABC (Paperback, Blue Back Book edition)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Dr. Seuss (지은이)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>8,410원</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>HarperCollins Publishers</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2017년 3월</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>구원의 ABC!</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>로탄 크리치만 (지은이)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>9,000원</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>BBCI(비비씨아이)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026년 3월</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Dr. Seuss's ABC (Hardcover)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>닥터 수스 (지은이)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>5,560원</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Random House</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1960년 8월</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Wipe-Clean 알파블록스 썼다 지웠다 ABC (스프링)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>펜그로하우스 편집부 (지은이)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>11,250원</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>펜그로하우스</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2022년 6월</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>글짓는 법 ABC : 처음 글쓰는 이들을 위하여</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>이태준 (지은이)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>컨텐츠코리아</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2017년 6월</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>i-dle (아이들) - 미니 9집 We made (Crow Ver.)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>i-dle (아이들)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>20,800원</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Kakao Entertainment</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026년 7월</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ABC 떼기 4</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>기탄교육 편집부 (엮은이)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>5,400원</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>기탄교육</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2008년 11월</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>의학통계 ABC</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>김수녕 (지은이)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>38,000원</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>군자출판사(교재)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2014년 11월</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>The ABC Murders (Paperback)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>애거사 크리스티 (지은이)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>12,800원</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Harper</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2013년 9월</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ABC 호텔: 노래하는 영어 동시</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>마리 앤 호버맨 (지은이) 말라 프레이지 (그림) 한지원 (옮긴이) Matthews Paul Richard Jaime Kim 정의택 윤은서 (낭독)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1,000원</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>윌북주니어</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2025년 10월</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>i-dle (아이들) - 미니 9집 We made (Mono Ver.)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>i-dle (아이들)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>19,300원</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Kakao Entertainment</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026년 7월</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>처음 시작하는 부동산경매 ABC</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>허명 (지은이)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>13,500원</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>무크랜드&amp;공인모</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2019년 10월</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>The ABC Book (Pokemon) (Hardcover)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Golden Books Steve Foxe (지은이)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>9,570원</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Golden books</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2020년 7월</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>바리스타의 ABC</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>백민지 (지은이)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>13,500원</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>아마디아</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2020년 10월</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>정영택의 설탕공예 ABC</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>정영택 (지은이)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>18,000원</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>교학사</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2007년 3월</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>고승덕의 ABCD 성공법</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>고승덕 (지은이)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>16,200원</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>마켓데일리주식회사(개미들)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2011년 11월</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ABC 떼기 5</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>기탄교육 편집부 (엮은이)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>5,400원</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>기탄교육</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2008년 11월</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>콕콕콕 사운드 벽보 : ABC</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>키움터 편집부 (엮은이)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>20,000원</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>키움터</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2022년 2월</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>한경무크 : 인생 리뉴얼 ABC</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>한국경제신문 및 한국경제매거진 특별취재팀 (지은이)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>18,000원</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>한국경제신문</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2022년 3월</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>정보교육의 ABC</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>이옥화 (지은이)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>22,000원</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>교육과학사</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2007년 9월</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>표정으로 배우는 ABC</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>솔트앤페퍼 (지은이)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>8,820원</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>소금과후추(킨더랜드)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2017년 3월</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>이해하면 보이는 어깨치료 ABC</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>조성형 (지은이)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>40,000원</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>군자출판사(교재)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2016년 8월</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>포켓몬스터W 한글*숫자*지혜*프로그래밍*ABC</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>학산문화사 편집부 (지은이)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>7,650원</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>학산문화사(단행본)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2021년 12월</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ABC for Me: ABC Yoga (Paperback)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Christiane Engel (지은이)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>14,370원</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>QUARTO PUBLISHING GROUP</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2022년 1월</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>통쾌한 희망사전</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>프레드릭 비크너 (지은이) 이문원 (옮긴이)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>12,600원</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>복있는사람</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026년 6월</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>전자기학의 ABC</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>후쿠시마 하지메 (지은이) 손영수 (옮긴이)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>6,300원</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>전파과학사</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2016년 11월</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ABC 떼기 6</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>기탄교육 편집부 (엮은이)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>5,400원</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>기탄교육</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2008년 11월</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>썼다 지웠다 ABC</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>지원 편집부 (지은이)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>7,650원</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>지원</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026년 4월</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ABC 떼기 7</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>기탄교육 편집부 (엮은이)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>5,400원</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>기탄교육</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2008년 12월</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>ABC Animals Adventure</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>최상미 (지은이)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>부크크</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026년 4월</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>구원의 ABC!</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>로탄 크리치만 (지은이)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>7,000원</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>BBCI(비비씨아이)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026년 4월</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Touch Think Learn : ABC (Board Books)</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Xavier Deneux (지은이)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>34,480원</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Chronicle Books Llc</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2016년 9월</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>i-dle (아이들) - 미니 9집 We made (POCAALBUM Ver.)</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>i-dle (아이들)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>13,400원</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Kakao Entertainment</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026년 7월</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>물리학의 ABC</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>후쿠시마 하지메 (지은이) 손영수 (옮긴이)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>12,350원</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>전파과학사</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2017년 12월</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>똑똑해지는 처음 하는 숨은그림찾기 : ABC</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>하이라이츠 편집부 (지은이)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>4,500원</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>아라미kids</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2021년 11월</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>초보자를 위한 바둑의 ABC</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>영산이랑 (지은이)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>4,500원</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>태을출판사(진화당)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2011년 10월</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>함께해요 수업나눔 ABC</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>터닝포인트 (지은이)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>19,800원</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>에듀니티</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2018년 11월</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>컬러링 ABC 알파벳</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>BIG PICTURE (지은이)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>9,000원</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>랭컴(Lancom)</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2023년 2월</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>ABC 살인 사건</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>애거서 크리스티 (지은이) 김남주 (옮긴이) 김현수 윤용식 김정훈 임진응 김인형 김용 이새벽 이자영 (낭독)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>14,000원</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>황금가지</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2019년 7월</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ABC Animals! (Hardcover)</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Rufus Butler Seder (지은이)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>22,320원</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Workman Pub Co</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2016년 10월</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Little Hands ABC Book</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>이퓨쳐 편집부 (지은이)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>15,300원</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>이퓨쳐</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2019년 10월</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Dr. Seuss's ABC Book &amp; CD [With CD] (Paperback)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>닥터 수스 Dr. Seuss (지은이)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>13,200원</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Random House Childrens Books</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2005년 1월</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ABC T-Rex (Paperback, Reprint)</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Bernard Most (지은이)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>15,970원</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Sandpiper</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2004년 4월</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>웹툰 ABC</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>윤기헌 김병수 이진희 최인수 임재환 이호 (지은이)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>20,000원</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>부산대학교출판문화원</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2021년 8월</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ABC 떼기 8</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>기탄교육 편집부 (엮은이)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>5,400원</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>기탄교육</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2008년 12월</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>현장 혁신을 위한 개선기법 ABC</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>김창남 (지은이)</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>11,700원</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>한국표준협회미디어</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2007년 6월</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>미니 깜찍 팝업북 ABC 세트 - 전7권</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>조현경 노란 (지은이) 삼식이 이수희 (그림)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>40,950원</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>꿈꾸는달팽이(꿈달)</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2022년 12월</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>우리 함께 ABC</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>코리나 루켄 (지은이) 김세실 (옮긴이)</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>15,300원</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>나는별</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2023년 7월</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>재미있는 ABC</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>EBS BOOKS 편집부 (지은이)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>8,100원</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>EBS BOOKS</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2020년 12월</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>EBS ELT Easy Learning (Book 1) My First ABCs</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>EBS (지은이)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>8,550원</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>한국교육방송공사(초등)</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2022년 8월</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>도포 입고 ABC 갓 쓰고 맨손체조</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>윤성렬 (지은이)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>9,000원</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>학민사</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2004년 9월</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>ABC 떼기 9</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>기탄교육 편집부 (엮은이)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>5,400원</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>기탄교육</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2008년 12월</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>인공지능 ABC</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>주해종 정화영 손병희 (지은이)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>26,000원</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>연두에디션</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026년 3월</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>ABC I Like Me! (Paperback)</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>낸시 칼슨 (지은이)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>8,240원</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Puffin</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>1999년 6월</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>ABC 떼기 10</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>기탄교육 편집부 (엮은이)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>5,400원</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>기탄교육</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2008년 12월</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>포레스텔라 - 정규 4집 THE LEGACY (주얼 Ver.)</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>포레스텔라 (Forestella)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>26,700원</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>소니뮤직(SonyMusic)</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026년 4월</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Bruno Munari's ABC (Hardcover, 6)</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>브루노 무나리 (지은이)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>34,200원</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Chronicle Books Llc</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2006년 3월</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>사회복지사를 위한 홍보 ABC</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>이경헌 (지은이)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>15,000원</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>커뮤니케이션북스</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2007년 8월</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>포레스텔라 - 정규 4집 THE LEGACY (도슨트북 Ver.)</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>포레스텔라 (Forestella)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>44,600원</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>소니뮤직(SonyMusic)</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026년 4월</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>통번역사 교육 ABC</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>L. K. 라티쉐프 V.I. 프로보토로프 (지은이) 방교영 (옮긴이)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>9,500원</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>한국외국어대학교출판부 지식출판원(HUINE)</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2013년 2월</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Tiny Talk ABC : Workbook (Paperback)</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>수잔 리버스 (지은이)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>11,050원</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Oxford(옥스포드)</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>1999년 4월</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>임상추론의 ABC : 환자를 볼까, 검사를 볼까?</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>니콜라 쿠퍼 존 프레인 (지은이) 윤병우 (옮긴이)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>25,000원</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>범문에듀케이션</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2018년 11월</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>숨바꼭질 ABC</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>김재영 (지은이)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>26,100원</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>현북스</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2025년 2월</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
